--- a/artfynd/A 52212-2025 artfynd.xlsx
+++ b/artfynd/A 52212-2025 artfynd.xlsx
@@ -12332,7 +12332,7 @@
         <v>125934885</v>
       </c>
       <c r="B121" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 52212-2025 artfynd.xlsx
+++ b/artfynd/A 52212-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125869099</v>
+        <v>125934407</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488911</v>
+        <v>488897</v>
       </c>
       <c r="R2" t="n">
-        <v>6818785</v>
+        <v>6818851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125869095</v>
+        <v>125934468</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489073</v>
+        <v>488919</v>
       </c>
       <c r="R3" t="n">
-        <v>6818667</v>
+        <v>6818878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125869094</v>
+        <v>125934687</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488911</v>
+        <v>488854</v>
       </c>
       <c r="R4" t="n">
-        <v>6818785</v>
+        <v>6818858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,66 +954,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125869113</v>
+        <v>125934770</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488135</v>
+        <v>488849</v>
       </c>
       <c r="R5" t="n">
-        <v>6819141</v>
+        <v>6818878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1040,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1060,66 +1051,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125869104</v>
+        <v>125937037</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488247</v>
+        <v>488431</v>
       </c>
       <c r="R6" t="n">
-        <v>6819048</v>
+        <v>6818719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1146,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125869102</v>
+        <v>125988566</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488917</v>
+        <v>488264</v>
       </c>
       <c r="R7" t="n">
-        <v>6818749</v>
+        <v>6818869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1243,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1263,66 +1245,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125869103</v>
+        <v>125988605</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488745</v>
+        <v>488257</v>
       </c>
       <c r="R8" t="n">
-        <v>6818841</v>
+        <v>6818880</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1349,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,66 +1342,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125869107</v>
+        <v>125869098</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488917</v>
+        <v>488974</v>
       </c>
       <c r="R9" t="n">
-        <v>6818749</v>
+        <v>6818775</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,54 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125869108</v>
+        <v>125934507</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488148</v>
+        <v>488909</v>
       </c>
       <c r="R10" t="n">
-        <v>6819146</v>
+        <v>6818877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125869098</v>
+        <v>125988993</v>
       </c>
       <c r="B11" t="n">
-        <v>80084</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488974</v>
+        <v>488223</v>
       </c>
       <c r="R11" t="n">
-        <v>6818775</v>
+        <v>6818937</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1678,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125869101</v>
+        <v>125989251</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,34 +1656,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488232</v>
+        <v>488207</v>
       </c>
       <c r="R12" t="n">
-        <v>6819052</v>
+        <v>6818985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,63 +1730,54 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125869118</v>
+        <v>125933758</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488159</v>
+        <v>488841</v>
       </c>
       <c r="R13" t="n">
         <v>6819005</v>
@@ -1861,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1881,57 +1827,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125869100</v>
+        <v>125933869</v>
       </c>
       <c r="B14" t="n">
-        <v>80083</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kruggfjället, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489073</v>
+        <v>488880</v>
       </c>
       <c r="R14" t="n">
-        <v>6818667</v>
+        <v>6818967</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1978,60 +1924,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonas Karlsson</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125934616</v>
+        <v>125986119</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488839</v>
+        <v>488459</v>
       </c>
       <c r="R15" t="n">
-        <v>6818918</v>
+        <v>6818981</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2055,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2075,60 +2021,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125936622</v>
+        <v>125869094</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488654</v>
+        <v>488911</v>
       </c>
       <c r="R16" t="n">
-        <v>6818633</v>
+        <v>6818785</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2152,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,57 +2118,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125936380</v>
+        <v>125869095</v>
       </c>
       <c r="B17" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488731</v>
+        <v>489073</v>
       </c>
       <c r="R17" t="n">
-        <v>6818773</v>
+        <v>6818667</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2249,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2269,60 +2215,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125936684</v>
+        <v>125934363</v>
       </c>
       <c r="B18" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488631</v>
+        <v>488904</v>
       </c>
       <c r="R18" t="n">
-        <v>6818621</v>
+        <v>6818858</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2378,48 +2324,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125935570</v>
+        <v>125934450</v>
       </c>
       <c r="B19" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488824</v>
+        <v>488874</v>
       </c>
       <c r="R19" t="n">
-        <v>6818805</v>
+        <v>6818886</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2463,60 +2409,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125936665</v>
+        <v>125934508</v>
       </c>
       <c r="B20" t="n">
-        <v>78738</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488458</v>
+        <v>488871</v>
       </c>
       <c r="R20" t="n">
-        <v>6818635</v>
+        <v>6818866</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2560,26 +2506,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125937533</v>
+        <v>125934616</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2603,17 +2549,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488556</v>
+        <v>488839</v>
       </c>
       <c r="R21" t="n">
-        <v>6818975</v>
+        <v>6818918</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2657,26 +2603,26 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125937741</v>
+        <v>125934683</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2704,13 +2650,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488731</v>
+        <v>488819</v>
       </c>
       <c r="R22" t="n">
-        <v>6818925</v>
+        <v>6818867</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2766,48 +2712,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125935502</v>
+        <v>125934762</v>
       </c>
       <c r="B23" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488799</v>
+        <v>488830</v>
       </c>
       <c r="R23" t="n">
-        <v>6818778</v>
+        <v>6818872</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2851,26 +2797,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125936168</v>
+        <v>125934910</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2894,17 +2840,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488761</v>
+        <v>488856</v>
       </c>
       <c r="R24" t="n">
-        <v>6818718</v>
+        <v>6818894</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2948,60 +2894,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125937321</v>
+        <v>125934942</v>
       </c>
       <c r="B25" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488500</v>
+        <v>488868</v>
       </c>
       <c r="R25" t="n">
-        <v>6818934</v>
+        <v>6818888</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3045,60 +2991,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125934921</v>
+        <v>125935283</v>
       </c>
       <c r="B26" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488878</v>
+        <v>488789</v>
       </c>
       <c r="R26" t="n">
-        <v>6818893</v>
+        <v>6818951</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3142,60 +3088,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125934407</v>
+        <v>125935364</v>
       </c>
       <c r="B27" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488897</v>
+        <v>488762</v>
       </c>
       <c r="R27" t="n">
-        <v>6818851</v>
+        <v>6818879</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3239,26 +3185,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125934762</v>
+        <v>125935403</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3282,17 +3228,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488830</v>
+        <v>488776</v>
       </c>
       <c r="R28" t="n">
-        <v>6818872</v>
+        <v>6818801</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3336,60 +3282,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125934507</v>
+        <v>125935463</v>
       </c>
       <c r="B29" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488909</v>
+        <v>488717</v>
       </c>
       <c r="R29" t="n">
-        <v>6818877</v>
+        <v>6818865</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3433,12 +3379,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3448,11 +3394,11 @@
         <v>125935510</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3542,48 +3488,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125937442</v>
+        <v>125935537</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488502</v>
+        <v>488681</v>
       </c>
       <c r="R31" t="n">
-        <v>6818988</v>
+        <v>6818862</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3613,11 +3559,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3632,44 +3573,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125937897</v>
+        <v>125935890</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3679,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488805</v>
+        <v>488720</v>
       </c>
       <c r="R32" t="n">
-        <v>6818928</v>
+        <v>6818836</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3715,11 +3656,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3746,14 +3682,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125936426</v>
+        <v>125936025</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3777,17 +3713,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488720</v>
+        <v>488845</v>
       </c>
       <c r="R33" t="n">
-        <v>6818745</v>
+        <v>6818675</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3831,60 +3767,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125934896</v>
+        <v>125936168</v>
       </c>
       <c r="B34" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488838</v>
+        <v>488761</v>
       </c>
       <c r="R34" t="n">
-        <v>6818893</v>
+        <v>6818718</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3914,11 +3850,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3933,60 +3864,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125934687</v>
+        <v>125936426</v>
       </c>
       <c r="B35" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488854</v>
+        <v>488720</v>
       </c>
       <c r="R35" t="n">
-        <v>6818858</v>
+        <v>6818745</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4030,60 +3961,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125935224</v>
+        <v>125936438</v>
       </c>
       <c r="B36" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488826</v>
+        <v>488735</v>
       </c>
       <c r="R36" t="n">
-        <v>6818956</v>
+        <v>6818743</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4127,26 +4058,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125934942</v>
+        <v>125936448</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4174,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488868</v>
+        <v>488720</v>
       </c>
       <c r="R37" t="n">
-        <v>6818888</v>
+        <v>6818724</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4236,48 +4167,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125934639</v>
+        <v>125936468</v>
       </c>
       <c r="B38" t="n">
-        <v>78386</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>488859</v>
+        <v>488715</v>
       </c>
       <c r="R38" t="n">
-        <v>6818878</v>
+        <v>6818694</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4321,60 +4252,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125933626</v>
+        <v>125936488</v>
       </c>
       <c r="B39" t="n">
-        <v>79569</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>488811</v>
+        <v>488717</v>
       </c>
       <c r="R39" t="n">
-        <v>6818985</v>
+        <v>6818649</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4418,26 +4349,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125934683</v>
+        <v>125936642</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4461,14 +4392,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>488819</v>
+        <v>488637</v>
       </c>
       <c r="R40" t="n">
-        <v>6818867</v>
+        <v>6818637</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4527,48 +4458,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125932883</v>
+        <v>125937533</v>
       </c>
       <c r="B41" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>488866</v>
+        <v>488556</v>
       </c>
       <c r="R41" t="n">
-        <v>6819050</v>
+        <v>6818975</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4624,14 +4555,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125935890</v>
+        <v>125937715</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4659,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>488720</v>
+        <v>488709</v>
       </c>
       <c r="R42" t="n">
-        <v>6818836</v>
+        <v>6818925</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4721,45 +4652,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125935014</v>
+        <v>125937741</v>
       </c>
       <c r="B43" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>488848</v>
+        <v>488731</v>
       </c>
       <c r="R43" t="n">
-        <v>6818924</v>
+        <v>6818925</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4806,26 +4737,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125937715</v>
+        <v>125983993</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4849,14 +4780,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>488709</v>
+        <v>488175</v>
       </c>
       <c r="R44" t="n">
-        <v>6818925</v>
+        <v>6819105</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4883,12 +4814,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4915,14 +4846,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125936468</v>
+        <v>125984038</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4946,14 +4877,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>488715</v>
+        <v>488196</v>
       </c>
       <c r="R45" t="n">
-        <v>6818694</v>
+        <v>6819100</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4980,12 +4911,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5012,48 +4943,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125934949</v>
+        <v>125984053</v>
       </c>
       <c r="B46" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>488893</v>
+        <v>488153</v>
       </c>
       <c r="R46" t="n">
-        <v>6818884</v>
+        <v>6819064</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5077,12 +5008,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5097,60 +5028,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125937037</v>
+        <v>125984097</v>
       </c>
       <c r="B47" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>488431</v>
+        <v>488144</v>
       </c>
       <c r="R47" t="n">
-        <v>6818719</v>
+        <v>6819011</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5174,12 +5105,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5194,57 +5125,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125937098</v>
+        <v>125984150</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>488445</v>
+        <v>488206</v>
       </c>
       <c r="R48" t="n">
-        <v>6818739</v>
+        <v>6819039</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5271,17 +5202,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5308,48 +5234,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125933869</v>
+        <v>125984672</v>
       </c>
       <c r="B49" t="n">
-        <v>91210</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>488880</v>
+        <v>488239</v>
       </c>
       <c r="R49" t="n">
-        <v>6818967</v>
+        <v>6818981</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5373,12 +5299,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5393,26 +5319,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125936438</v>
+        <v>125984809</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5436,14 +5362,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>488735</v>
+        <v>488249</v>
       </c>
       <c r="R50" t="n">
-        <v>6818743</v>
+        <v>6818977</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5470,12 +5396,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5502,14 +5428,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125935403</v>
+        <v>125986756</v>
       </c>
       <c r="B51" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5533,17 +5459,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>488776</v>
+        <v>488530</v>
       </c>
       <c r="R51" t="n">
-        <v>6818801</v>
+        <v>6818904</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5567,12 +5493,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5587,44 +5513,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125934770</v>
+        <v>125986848</v>
       </c>
       <c r="B52" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5634,13 +5560,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>488849</v>
+        <v>488497</v>
       </c>
       <c r="R52" t="n">
-        <v>6818878</v>
+        <v>6818890</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5664,12 +5590,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5684,57 +5610,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125934563</v>
+        <v>125987243</v>
       </c>
       <c r="B53" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>488882</v>
+        <v>488354</v>
       </c>
       <c r="R53" t="n">
-        <v>6818866</v>
+        <v>6818765</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5761,12 +5687,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5793,45 +5719,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125933949</v>
+        <v>125988445</v>
       </c>
       <c r="B54" t="n">
-        <v>79598</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>488891</v>
+        <v>488400</v>
       </c>
       <c r="R54" t="n">
-        <v>6818946</v>
+        <v>6818592</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5858,12 +5784,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5890,14 +5816,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125935283</v>
+        <v>125988482</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -5921,17 +5847,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>488789</v>
+        <v>488376</v>
       </c>
       <c r="R55" t="n">
-        <v>6818951</v>
+        <v>6818620</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5955,12 +5881,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5987,14 +5913,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125936448</v>
+        <v>125988494</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6018,14 +5944,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>488720</v>
+        <v>488368</v>
       </c>
       <c r="R56" t="n">
-        <v>6818724</v>
+        <v>6818606</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6052,12 +5978,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6084,45 +6010,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125934886</v>
+        <v>125988725</v>
       </c>
       <c r="B57" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>488849</v>
+        <v>488252</v>
       </c>
       <c r="R57" t="n">
-        <v>6818891</v>
+        <v>6818905</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6149,12 +6075,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6181,45 +6107,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125935216</v>
+        <v>125988735</v>
       </c>
       <c r="B58" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>488832</v>
+        <v>488266</v>
       </c>
       <c r="R58" t="n">
-        <v>6818964</v>
+        <v>6818782</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6246,12 +6172,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6278,14 +6204,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125934508</v>
+        <v>125988871</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6309,14 +6235,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>488871</v>
+        <v>488271</v>
       </c>
       <c r="R59" t="n">
-        <v>6818866</v>
+        <v>6818822</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6343,12 +6269,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6375,14 +6301,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125934450</v>
+        <v>125989221</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6406,17 +6332,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>488874</v>
+        <v>488211</v>
       </c>
       <c r="R60" t="n">
-        <v>6818886</v>
+        <v>6818972</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6440,12 +6366,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6460,22 +6386,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125934468</v>
+        <v>125934639</v>
       </c>
       <c r="B61" t="n">
-        <v>78647</v>
+        <v>78730</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6483,21 +6409,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6507,13 +6433,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>488919</v>
+        <v>488859</v>
       </c>
       <c r="R61" t="n">
         <v>6818878</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6569,32 +6495,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125933758</v>
+        <v>125934604</v>
       </c>
       <c r="B62" t="n">
-        <v>91210</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6604,10 +6530,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>488841</v>
+        <v>488864</v>
       </c>
       <c r="R62" t="n">
-        <v>6819005</v>
+        <v>6818878</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6666,10 +6592,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125934604</v>
+        <v>125936665</v>
       </c>
       <c r="B63" t="n">
-        <v>78738</v>
+        <v>79084</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6697,14 +6623,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>488864</v>
+        <v>488458</v>
       </c>
       <c r="R63" t="n">
-        <v>6818878</v>
+        <v>6818635</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6763,10 +6689,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125935537</v>
+        <v>125985190</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>79084</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6774,37 +6700,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>488681</v>
+        <v>488327</v>
       </c>
       <c r="R64" t="n">
-        <v>6818862</v>
+        <v>6818968</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6828,12 +6754,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6848,22 +6774,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125934399</v>
+        <v>125986131</v>
       </c>
       <c r="B65" t="n">
-        <v>79598</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6871,37 +6797,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>488895</v>
+        <v>488444</v>
       </c>
       <c r="R65" t="n">
-        <v>6818859</v>
+        <v>6818918</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6925,12 +6851,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6945,22 +6871,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125934910</v>
+        <v>125986685</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6968,34 +6894,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>488856</v>
+        <v>488505</v>
       </c>
       <c r="R66" t="n">
-        <v>6818894</v>
+        <v>6818935</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7022,12 +6948,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7054,10 +6980,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125936025</v>
+        <v>125987994</v>
       </c>
       <c r="B67" t="n">
-        <v>78980</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7065,21 +6991,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7089,13 +7015,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>488845</v>
+        <v>488450</v>
       </c>
       <c r="R67" t="n">
-        <v>6818675</v>
+        <v>6818611</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7119,12 +7045,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7139,22 +7065,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125935463</v>
+        <v>125932883</v>
       </c>
       <c r="B68" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7162,37 +7088,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>488717</v>
+        <v>488866</v>
       </c>
       <c r="R68" t="n">
-        <v>6818865</v>
+        <v>6819050</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7236,22 +7162,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125935887</v>
+        <v>125933949</v>
       </c>
       <c r="B69" t="n">
-        <v>57657</v>
+        <v>79946</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7259,37 +7185,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>488851</v>
+        <v>488891</v>
       </c>
       <c r="R69" t="n">
-        <v>6818708</v>
+        <v>6818946</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7319,11 +7245,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7338,22 +7259,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125934739</v>
+        <v>125934399</v>
       </c>
       <c r="B70" t="n">
-        <v>78739</v>
+        <v>79946</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7361,21 +7282,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7385,10 +7306,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>488860</v>
+        <v>488895</v>
       </c>
       <c r="R70" t="n">
-        <v>6818868</v>
+        <v>6818859</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7447,10 +7368,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125934234</v>
+        <v>125934563</v>
       </c>
       <c r="B71" t="n">
-        <v>78739</v>
+        <v>79946</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7458,37 +7379,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>488859</v>
+        <v>488882</v>
       </c>
       <c r="R71" t="n">
-        <v>6818886</v>
+        <v>6818866</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7532,22 +7453,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125936447</v>
+        <v>125934928</v>
       </c>
       <c r="B72" t="n">
-        <v>79598</v>
+        <v>79946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7575,17 +7496,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>488656</v>
+        <v>488878</v>
       </c>
       <c r="R72" t="n">
-        <v>6818762</v>
+        <v>6818892</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7641,10 +7562,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125936488</v>
+        <v>125935014</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7652,37 +7573,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>488717</v>
+        <v>488848</v>
       </c>
       <c r="R73" t="n">
-        <v>6818649</v>
+        <v>6818924</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7726,22 +7647,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125935364</v>
+        <v>125935224</v>
       </c>
       <c r="B74" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7749,37 +7670,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>488762</v>
+        <v>488826</v>
       </c>
       <c r="R74" t="n">
-        <v>6818879</v>
+        <v>6818956</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7823,22 +7744,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125934928</v>
+        <v>125935502</v>
       </c>
       <c r="B75" t="n">
-        <v>79598</v>
+        <v>79946</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7866,17 +7787,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>488878</v>
+        <v>488799</v>
       </c>
       <c r="R75" t="n">
-        <v>6818892</v>
+        <v>6818778</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7932,10 +7853,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125932852</v>
+        <v>125936447</v>
       </c>
       <c r="B76" t="n">
-        <v>78739</v>
+        <v>79946</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7943,37 +7864,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>488802</v>
+        <v>488656</v>
       </c>
       <c r="R76" t="n">
-        <v>6819049</v>
+        <v>6818762</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8017,22 +7938,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125935420</v>
+        <v>125869099</v>
       </c>
       <c r="B77" t="n">
-        <v>78739</v>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8040,37 +7961,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>488729</v>
+        <v>488911</v>
       </c>
       <c r="R77" t="n">
-        <v>6818892</v>
+        <v>6818785</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8094,12 +8015,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8114,22 +8035,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125936642</v>
+        <v>125869100</v>
       </c>
       <c r="B78" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8137,37 +8058,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>488637</v>
+        <v>489073</v>
       </c>
       <c r="R78" t="n">
-        <v>6818637</v>
+        <v>6818667</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8191,12 +8112,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8211,60 +8132,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125935851</v>
+        <v>125869101</v>
       </c>
       <c r="B79" t="n">
-        <v>58334</v>
+        <v>80432</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103044</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>488704</v>
+        <v>488232</v>
       </c>
       <c r="R79" t="n">
-        <v>6818845</v>
+        <v>6819052</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8288,12 +8209,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8308,22 +8229,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125934363</v>
+        <v>125869102</v>
       </c>
       <c r="B80" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8331,34 +8252,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>488904</v>
+        <v>488917</v>
       </c>
       <c r="R80" t="n">
-        <v>6818858</v>
+        <v>6818749</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8385,12 +8306,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8405,22 +8326,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125936503</v>
+        <v>125984501</v>
       </c>
       <c r="B81" t="n">
-        <v>78739</v>
+        <v>80432</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8428,34 +8349,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>488698</v>
+        <v>488242</v>
       </c>
       <c r="R81" t="n">
-        <v>6818639</v>
+        <v>6819007</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -8482,12 +8403,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8514,10 +8435,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125989251</v>
+        <v>125988835</v>
       </c>
       <c r="B82" t="n">
-        <v>91265</v>
+        <v>80432</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8525,21 +8446,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8549,10 +8470,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>488207</v>
+        <v>488237</v>
       </c>
       <c r="R82" t="n">
-        <v>6818985</v>
+        <v>6818903</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8611,10 +8532,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125984809</v>
+        <v>125934885</v>
       </c>
       <c r="B83" t="n">
-        <v>78980</v>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8622,37 +8543,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>488249</v>
+        <v>488847</v>
       </c>
       <c r="R83" t="n">
-        <v>6818977</v>
+        <v>6818885</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8676,12 +8597,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8708,10 +8629,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125984501</v>
+        <v>125934896</v>
       </c>
       <c r="B84" t="n">
-        <v>80083</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8719,37 +8640,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>488242</v>
+        <v>488838</v>
       </c>
       <c r="R84" t="n">
-        <v>6819007</v>
+        <v>6818893</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8773,12 +8694,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8805,10 +8731,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125984672</v>
+        <v>125935887</v>
       </c>
       <c r="B85" t="n">
-        <v>78980</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8816,21 +8742,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8840,13 +8766,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>488239</v>
+        <v>488851</v>
       </c>
       <c r="R85" t="n">
-        <v>6818981</v>
+        <v>6818708</v>
       </c>
       <c r="S85" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8870,12 +8796,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8890,22 +8821,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125986756</v>
+        <v>125936622</v>
       </c>
       <c r="B86" t="n">
-        <v>78980</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8913,34 +8844,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>488530</v>
+        <v>488654</v>
       </c>
       <c r="R86" t="n">
-        <v>6818904</v>
+        <v>6818633</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -8967,12 +8898,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -8999,10 +8930,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125986685</v>
+        <v>125937098</v>
       </c>
       <c r="B87" t="n">
-        <v>78738</v>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9010,34 +8941,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>488505</v>
+        <v>488445</v>
       </c>
       <c r="R87" t="n">
-        <v>6818935</v>
+        <v>6818739</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9064,12 +8995,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9096,10 +9032,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125988566</v>
+        <v>125937442</v>
       </c>
       <c r="B88" t="n">
-        <v>78647</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9107,34 +9043,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>488264</v>
+        <v>488502</v>
       </c>
       <c r="R88" t="n">
-        <v>6818869</v>
+        <v>6818988</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9161,12 +9097,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9193,10 +9134,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125986131</v>
+        <v>125937897</v>
       </c>
       <c r="B89" t="n">
-        <v>78738</v>
+        <v>57953</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9204,34 +9145,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>488444</v>
+        <v>488805</v>
       </c>
       <c r="R89" t="n">
-        <v>6818918</v>
+        <v>6818928</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9258,12 +9199,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9290,10 +9236,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125988871</v>
+        <v>125989551</v>
       </c>
       <c r="B90" t="n">
-        <v>78980</v>
+        <v>57953</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9301,34 +9247,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>488271</v>
+        <v>488103</v>
       </c>
       <c r="R90" t="n">
-        <v>6818822</v>
+        <v>6819049</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9361,6 +9307,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färskt ringhack.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9387,57 +9338,56 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125984440</v>
+        <v>133184957</v>
       </c>
       <c r="B91" t="n">
-        <v>98395</v>
+        <v>57975</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>488244</v>
+        <v>488246</v>
       </c>
       <c r="R91" t="n">
-        <v>6819028</v>
+        <v>6819214</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9461,12 +9411,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9481,22 +9431,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125988445</v>
+        <v>133185022</v>
       </c>
       <c r="B92" t="n">
-        <v>78980</v>
+        <v>57975</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9504,37 +9454,45 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>488400</v>
+        <v>488257</v>
       </c>
       <c r="R92" t="n">
-        <v>6818592</v>
+        <v>6819197</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9558,12 +9516,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9578,22 +9541,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125987243</v>
+        <v>133185033</v>
       </c>
       <c r="B93" t="n">
-        <v>78980</v>
+        <v>57975</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9601,34 +9564,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Lills Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>488354</v>
+        <v>488243</v>
       </c>
       <c r="R93" t="n">
-        <v>6818765</v>
+        <v>6819207</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9655,12 +9626,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9675,22 +9646,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125989085</v>
+        <v>133185051</v>
       </c>
       <c r="B94" t="n">
-        <v>78739</v>
+        <v>57975</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9698,37 +9669,45 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>488202</v>
+        <v>488242</v>
       </c>
       <c r="R94" t="n">
-        <v>6818963</v>
+        <v>6819200</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9752,12 +9731,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9772,22 +9751,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125984038</v>
+        <v>133185133</v>
       </c>
       <c r="B95" t="n">
-        <v>78980</v>
+        <v>57975</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9795,37 +9774,45 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>488196</v>
+        <v>488252</v>
       </c>
       <c r="R95" t="n">
-        <v>6819100</v>
+        <v>6819189</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9849,12 +9836,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9869,60 +9856,60 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125986119</v>
+        <v>125987019</v>
       </c>
       <c r="B96" t="n">
-        <v>91210</v>
+        <v>58114</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>488459</v>
+        <v>488514</v>
       </c>
       <c r="R96" t="n">
-        <v>6818981</v>
+        <v>6818802</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9966,57 +9953,57 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125988735</v>
+        <v>125935851</v>
       </c>
       <c r="B97" t="n">
-        <v>78980</v>
+        <v>58636</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>488266</v>
+        <v>488704</v>
       </c>
       <c r="R97" t="n">
-        <v>6818782</v>
+        <v>6818845</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10043,12 +10030,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10075,45 +10062,54 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125984150</v>
+        <v>125984338</v>
       </c>
       <c r="B98" t="n">
-        <v>78980</v>
+        <v>99153</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>488206</v>
+        <v>488234</v>
       </c>
       <c r="R98" t="n">
-        <v>6819039</v>
+        <v>6819040</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10172,48 +10168,57 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125988835</v>
+        <v>125984440</v>
       </c>
       <c r="B99" t="n">
-        <v>80083</v>
+        <v>99153</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>488237</v>
+        <v>488244</v>
       </c>
       <c r="R99" t="n">
-        <v>6818903</v>
+        <v>6819028</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10257,57 +10262,66 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125988482</v>
+        <v>125989375</v>
       </c>
       <c r="B100" t="n">
-        <v>78980</v>
+        <v>99153</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>488376</v>
+        <v>488248</v>
       </c>
       <c r="R100" t="n">
-        <v>6818620</v>
+        <v>6819009</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -10366,45 +10380,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125989221</v>
+        <v>125869103</v>
       </c>
       <c r="B101" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>488211</v>
+        <v>488745</v>
       </c>
       <c r="R101" t="n">
-        <v>6818972</v>
+        <v>6818841</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10431,12 +10454,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10451,57 +10474,66 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125986843</v>
+        <v>125869104</v>
       </c>
       <c r="B102" t="n">
-        <v>78739</v>
+        <v>99118</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>488440</v>
+        <v>488247</v>
       </c>
       <c r="R102" t="n">
-        <v>6818890</v>
+        <v>6819048</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10528,12 +10560,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10548,60 +10580,69 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125985280</v>
+        <v>125869107</v>
       </c>
       <c r="B103" t="n">
-        <v>78739</v>
+        <v>99118</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>488376</v>
+        <v>488917</v>
       </c>
       <c r="R103" t="n">
-        <v>6818970</v>
+        <v>6818749</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10625,12 +10666,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10645,60 +10686,69 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125985181</v>
+        <v>125869108</v>
       </c>
       <c r="B104" t="n">
-        <v>78739</v>
+        <v>99118</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>488320</v>
+        <v>488148</v>
       </c>
       <c r="R104" t="n">
-        <v>6818956</v>
+        <v>6819146</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10722,12 +10772,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10742,60 +10792,69 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125986283</v>
+        <v>125869113</v>
       </c>
       <c r="B105" t="n">
-        <v>78739</v>
+        <v>99118</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>488483</v>
+        <v>488135</v>
       </c>
       <c r="R105" t="n">
-        <v>6818970</v>
+        <v>6819141</v>
       </c>
       <c r="S105" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10819,12 +10878,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10839,60 +10898,69 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125988576</v>
+        <v>125869118</v>
       </c>
       <c r="B106" t="n">
-        <v>78739</v>
+        <v>99118</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Kruggfjället, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>488336</v>
+        <v>488159</v>
       </c>
       <c r="R106" t="n">
-        <v>6818701</v>
+        <v>6819005</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10916,12 +10984,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10936,22 +11004,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Jonas Karlsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125988605</v>
+        <v>125932852</v>
       </c>
       <c r="B107" t="n">
-        <v>78647</v>
+        <v>79085</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10959,37 +11027,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>488257</v>
+        <v>488802</v>
       </c>
       <c r="R107" t="n">
-        <v>6818880</v>
+        <v>6819049</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11013,12 +11081,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11033,22 +11101,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125988494</v>
+        <v>125934234</v>
       </c>
       <c r="B108" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11056,34 +11124,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>488368</v>
+        <v>488859</v>
       </c>
       <c r="R108" t="n">
-        <v>6818606</v>
+        <v>6818886</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -11110,12 +11178,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11142,10 +11210,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125986848</v>
+        <v>125934739</v>
       </c>
       <c r="B109" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11153,21 +11221,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11177,13 +11245,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>488497</v>
+        <v>488860</v>
       </c>
       <c r="R109" t="n">
-        <v>6818890</v>
+        <v>6818868</v>
       </c>
       <c r="S109" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11207,12 +11275,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11227,22 +11295,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125989551</v>
+        <v>125934886</v>
       </c>
       <c r="B110" t="n">
-        <v>57657</v>
+        <v>79085</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11250,37 +11318,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>488103</v>
+        <v>488849</v>
       </c>
       <c r="R110" t="n">
-        <v>6819049</v>
+        <v>6818891</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11304,17 +11372,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Färskt ringhack.</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11329,22 +11392,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125985190</v>
+        <v>125934921</v>
       </c>
       <c r="B111" t="n">
-        <v>78738</v>
+        <v>79085</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11352,37 +11415,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>488327</v>
+        <v>488878</v>
       </c>
       <c r="R111" t="n">
-        <v>6818968</v>
+        <v>6818893</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11406,12 +11469,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11438,10 +11501,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125983993</v>
+        <v>125934949</v>
       </c>
       <c r="B112" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11449,37 +11512,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>488175</v>
+        <v>488893</v>
       </c>
       <c r="R112" t="n">
-        <v>6819105</v>
+        <v>6818884</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11503,12 +11566,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11523,22 +11586,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125987019</v>
+        <v>125935216</v>
       </c>
       <c r="B113" t="n">
-        <v>57817</v>
+        <v>79085</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11546,34 +11609,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Herostjärnen, Herostjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>488514</v>
+        <v>488832</v>
       </c>
       <c r="R113" t="n">
-        <v>6818802</v>
+        <v>6818964</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -11600,12 +11663,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11632,10 +11695,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125987994</v>
+        <v>125935420</v>
       </c>
       <c r="B114" t="n">
-        <v>78738</v>
+        <v>79085</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11643,34 +11706,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
+          <t>Flyna, Flyna, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>488450</v>
+        <v>488729</v>
       </c>
       <c r="R114" t="n">
-        <v>6818611</v>
+        <v>6818892</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -11697,12 +11760,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11729,57 +11792,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125989375</v>
+        <v>125935570</v>
       </c>
       <c r="B115" t="n">
-        <v>98395</v>
+        <v>79085</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219874</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>488248</v>
+        <v>488824</v>
       </c>
       <c r="R115" t="n">
-        <v>6819009</v>
+        <v>6818805</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11803,12 +11857,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11823,69 +11877,60 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125984338</v>
+        <v>125936380</v>
       </c>
       <c r="B116" t="n">
-        <v>98395</v>
+        <v>79085</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219874</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>488234</v>
+        <v>488731</v>
       </c>
       <c r="R116" t="n">
-        <v>6819040</v>
+        <v>6818773</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11909,12 +11954,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11929,60 +11974,60 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125988993</v>
+        <v>125936503</v>
       </c>
       <c r="B117" t="n">
-        <v>92535</v>
+        <v>79085</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>488223</v>
+        <v>488698</v>
       </c>
       <c r="R117" t="n">
-        <v>6818937</v>
+        <v>6818639</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12006,12 +12051,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12026,22 +12071,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125984097</v>
+        <v>125936684</v>
       </c>
       <c r="B118" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12049,34 +12094,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>488144</v>
+        <v>488631</v>
       </c>
       <c r="R118" t="n">
-        <v>6819011</v>
+        <v>6818621</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -12103,12 +12148,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12135,10 +12180,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125984053</v>
+        <v>125937321</v>
       </c>
       <c r="B119" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12146,34 +12191,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
+          <t>Kruggfjällstjärnen, Kruggfjällstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>488153</v>
+        <v>488500</v>
       </c>
       <c r="R119" t="n">
-        <v>6819064</v>
+        <v>6818934</v>
       </c>
       <c r="S119" t="n">
         <v>20</v>
@@ -12200,12 +12245,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12220,22 +12265,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125988725</v>
+        <v>125985181</v>
       </c>
       <c r="B120" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12243,21 +12288,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12267,13 +12312,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>488252</v>
+        <v>488320</v>
       </c>
       <c r="R120" t="n">
-        <v>6818905</v>
+        <v>6818956</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12317,22 +12362,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125934885</v>
+        <v>125985280</v>
       </c>
       <c r="B121" t="n">
-        <v>57661</v>
+        <v>79085</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12340,37 +12385,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Flyna, Flyna, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>488847</v>
+        <v>488376</v>
       </c>
       <c r="R121" t="n">
-        <v>6818885</v>
+        <v>6818970</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12394,12 +12439,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12426,10 +12471,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133185022</v>
+        <v>125986283</v>
       </c>
       <c r="B122" t="n">
-        <v>57965</v>
+        <v>79085</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12437,45 +12482,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>488257</v>
+        <v>488483</v>
       </c>
       <c r="R122" t="n">
-        <v>6819197</v>
+        <v>6818970</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12499,17 +12536,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar.</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12524,22 +12556,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133185033</v>
+        <v>125986843</v>
       </c>
       <c r="B123" t="n">
-        <v>57965</v>
+        <v>79085</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12547,42 +12579,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Lills Sildakorvamägg, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>488243</v>
+        <v>488440</v>
       </c>
       <c r="R123" t="n">
-        <v>6819207</v>
+        <v>6818890</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12609,12 +12633,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12629,22 +12653,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133184957</v>
+        <v>125988576</v>
       </c>
       <c r="B124" t="n">
-        <v>57965</v>
+        <v>79085</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12652,45 +12676,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>488246</v>
+        <v>488336</v>
       </c>
       <c r="R124" t="n">
-        <v>6819214</v>
+        <v>6818701</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12714,12 +12730,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12734,22 +12750,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133185051</v>
+        <v>125989085</v>
       </c>
       <c r="B125" t="n">
-        <v>57965</v>
+        <v>79085</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12757,45 +12773,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Dlr</t>
+          <t>Lilla Sildakorvamägg, Lilla Sildakorvamägg, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>488242</v>
+        <v>488202</v>
       </c>
       <c r="R125" t="n">
-        <v>6819200</v>
+        <v>6818963</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12819,12 +12827,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12839,22 +12847,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133185133</v>
+        <v>125933626</v>
       </c>
       <c r="B126" t="n">
-        <v>57965</v>
+        <v>79917</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12862,42 +12870,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lilla Sildakorvamägg, Dlr</t>
+          <t>Herostjärnen, Herostjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>488252</v>
+        <v>488811</v>
       </c>
       <c r="R126" t="n">
-        <v>6819189</v>
+        <v>6818985</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12924,12 +12924,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -12944,12 +12944,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>

--- a/artfynd/A 52212-2025 artfynd.xlsx
+++ b/artfynd/A 52212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AZ126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934407</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934468</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934687</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934770</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125937037</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988566</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988605</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869098</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934507</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988993</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125989251</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125933758</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125933869</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125986119</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869094</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869095</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934363</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934450</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934508</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934616</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934683</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934762</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934910</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934942</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935283</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935364</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935403</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935463</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935510</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935537</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935890</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936168</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936426</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936438</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936448</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936468</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936488</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936642</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125937533</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125937715</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125937741</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125983993</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984038</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984053</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984097</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984150</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984672</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,6 +5670,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984809</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5522,6 +5772,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125986756</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5619,6 +5874,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125986848</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5716,6 +5976,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125987243</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5813,6 +6078,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988445</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5910,6 +6180,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988482</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6007,6 +6282,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988494</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6104,6 +6384,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988725</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6201,6 +6486,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988735</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6298,6 +6588,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988871</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6395,6 +6690,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125989221</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6492,6 +6792,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934639</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6589,6 +6894,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934604</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6686,6 +6996,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936665</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6783,6 +7098,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125985190</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6880,6 +7200,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125986131</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6977,6 +7302,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125986685</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7074,6 +7404,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125987994</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7171,6 +7506,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932883</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7268,6 +7608,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125933949</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7365,6 +7710,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934399</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7462,6 +7812,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934563</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7559,6 +7914,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934928</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7656,6 +8016,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935014</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7753,6 +8118,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935224</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7850,6 +8220,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935502</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7947,6 +8322,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936447</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8044,6 +8424,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869099</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8141,6 +8526,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869100</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8238,6 +8628,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869101</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8335,6 +8730,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869102</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8432,6 +8832,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984501</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8529,6 +8934,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988835</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8626,6 +9036,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934885</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8728,6 +9143,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934896</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8830,6 +9250,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935887</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8927,6 +9352,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936622</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9029,6 +9459,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125937098</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9131,6 +9566,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125937442</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9233,6 +9673,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125937897</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9335,6 +9780,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125989551</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9440,6 +9890,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133184957</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9550,6 +10005,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133185022</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9655,6 +10115,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133185033</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9760,6 +10225,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133185051</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9865,6 +10335,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133185133</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9962,6 +10437,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125987019</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10059,6 +10539,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935851</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10165,6 +10650,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984338</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10271,6 +10761,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984440</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10377,6 +10872,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125989375</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10483,6 +10983,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869103</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10589,6 +11094,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869104</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10695,6 +11205,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869107</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10801,6 +11316,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869108</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10907,6 +11427,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869113</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11013,6 +11538,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125869118</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11110,6 +11640,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125932852</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11207,6 +11742,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934234</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11304,6 +11844,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934739</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11401,6 +11946,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934886</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11498,6 +12048,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934921</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11595,6 +12150,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125934949</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11692,6 +12252,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935216</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11789,6 +12354,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935420</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11886,6 +12456,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125935570</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11983,6 +12558,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936380</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12080,6 +12660,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936503</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12177,6 +12762,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125936684</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12274,6 +12864,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125937321</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12371,6 +12966,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125985181</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12468,6 +13068,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125985280</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12565,6 +13170,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125986283</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12662,6 +13272,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125986843</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12759,6 +13374,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988576</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12856,6 +13476,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125989085</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12953,8 +13578,140 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125933626</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>